--- a/data/trans_orig/P37A$medicootras-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P37A$medicootras-Clase-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9919</t>
+          <t>9532</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10162</t>
+          <t>9621</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>463857</t>
+          <t>464244</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>770295</t>
+          <t>770836</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6006</t>
+          <t>5998</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6175</t>
+          <t>6205</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>886</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8528</t>
+          <t>9371</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>360928</t>
+          <t>360936</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>365690</t>
+          <t>365660</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>730271</t>
+          <t>729428</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>737912</t>
+          <t>737913</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6842</t>
+          <t>6316</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7074</t>
+          <t>7071</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9739</t>
+          <t>9975</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>535547</t>
+          <t>536073</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>160708</t>
+          <t>160711</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>700432</t>
+          <t>700196</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>709151</t>
+          <t>709147</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4275</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6211</t>
+          <t>7074</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>848</t>
+          <t>849</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8339</t>
+          <t>7709</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1234059</t>
+          <t>1234122</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>708074</t>
+          <t>707211</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1944281</t>
+          <t>1944911</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1951772</t>
+          <t>1951771</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6932</t>
+          <t>6873</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5948</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>561820</t>
+          <t>561879</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>913359</t>
+          <t>911860</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5740</t>
+          <t>4731</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5441</t>
+          <t>4787</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,31%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>292461</t>
+          <t>293470</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1541519</t>
+          <t>1542173</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2915</t>
+          <t>3522</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15645</t>
+          <t>16015</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,44 +2806,44 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>7219</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>2988</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>14305</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
           <t>0,09%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>7219</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>2966</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>14137</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
           <t>0,42%</t>
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8321</t>
+          <t>8393</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23236</t>
+          <t>23853</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3254545</t>
+          <t>3254175</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3267275</t>
+          <t>3266668</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,49 +2919,49 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>99,89%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>3289</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>3370905</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>3363819</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3375136</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>99,79%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>99,58%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
           <t>99,91%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>3289</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>3370905</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>3363987</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>3375158</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,79%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>99,58%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>99,91%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>6489</t>
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6625078</t>
+          <t>6624461</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6639993</t>
+          <t>6639921</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9976</t>
+          <t>9983</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9883</t>
+          <t>11519</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13894</t>
+          <t>14513</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>427235</t>
+          <t>427228</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>304571</t>
+          <t>302935</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>737771</t>
+          <t>737152</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>750615</t>
+          <t>750627</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11899</t>
+          <t>11608</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>891</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>7865</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13113</t>
+          <t>14270</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>406898</t>
+          <t>407189</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>329812</t>
+          <t>330146</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>337130</t>
+          <t>337120</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>743695</t>
+          <t>742538</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>754922</t>
+          <t>754835</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7409</t>
+          <t>6755</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12836</t>
+          <t>13244</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13293</t>
+          <t>13276</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>622006</t>
+          <t>622660</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>247293</t>
+          <t>246885</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>876251</t>
+          <t>876268</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>888473</t>
+          <t>888480</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2774</t>
+          <t>2784</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12794</t>
+          <t>13806</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>940</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8320</t>
+          <t>7801</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4753</t>
+          <t>4603</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17385</t>
+          <t>16507</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1146215</t>
+          <t>1145203</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1156235</t>
+          <t>1156225</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>758337</t>
+          <t>758856</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>765713</t>
+          <t>765717</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1908282</t>
+          <t>1909160</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1920914</t>
+          <t>1921064</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>5868</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>1124</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9604</t>
+          <t>8921</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1932</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11444</t>
+          <t>11918</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>505118</t>
+          <t>504728</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>751918</t>
+          <t>752601</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>760540</t>
+          <t>760398</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1260674</t>
+          <t>1260200</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1270186</t>
+          <t>1270195</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8306</t>
+          <t>8203</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5394</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18106</t>
+          <t>19277</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6968</t>
+          <t>6630</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22042</t>
+          <t>22526</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>258576</t>
+          <t>258679</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1091245</t>
+          <t>1090074</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1104121</t>
+          <t>1103957</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1354191</t>
+          <t>1353707</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1369265</t>
+          <t>1369603</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10319</t>
+          <t>9453</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>28560</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16505</t>
+          <t>17294</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>38370</t>
+          <t>38982</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30191</t>
+          <t>30381</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>58607</t>
+          <t>58139</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3391970</t>
+          <t>3393350</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3411591</t>
+          <t>3412457</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3511755</t>
+          <t>3511143</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3533620</t>
+          <t>3532831</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6913428</t>
+          <t>6913896</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6941844</t>
+          <t>6941654</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6451</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>988</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8793</t>
+          <t>8953</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>422382</t>
+          <t>422551</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>340604</t>
+          <t>340784</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>767354</t>
+          <t>767194</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>775146</t>
+          <t>775159</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9575</t>
+          <t>9623</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7780</t>
+          <t>6874</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11377</t>
+          <t>12174</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>367652</t>
+          <t>367604</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>364493</t>
+          <t>365399</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>738123</t>
+          <t>737326</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>747462</t>
+          <t>747533</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>4944</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4535</t>
+          <t>5937</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -6802,7 +6802,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>516413</t>
+          <t>516970</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>683501</t>
+          <t>682099</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>4964</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17673</t>
+          <t>18053</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>4504</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17269</t>
+          <t>16795</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11928</t>
+          <t>12135</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30206</t>
+          <t>30769</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1131965</t>
+          <t>1131585</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1144389</t>
+          <t>1144674</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>808607</t>
+          <t>809081</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>821167</t>
+          <t>821372</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1945308</t>
+          <t>1944745</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1963586</t>
+          <t>1963379</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7614</t>
+          <t>9850</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1829</t>
+          <t>1821</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11746</t>
+          <t>12575</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2316</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14772</t>
+          <t>15436</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -7488,7 +7488,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>613092</t>
+          <t>610856</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>726498</t>
+          <t>725669</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>736415</t>
+          <t>736423</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1344178</t>
+          <t>1343514</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1356634</t>
+          <t>1356521</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,82%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5305</t>
+          <t>6366</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9988</t>
+          <t>9247</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1820</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11021</t>
+          <t>11072</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>281840</t>
+          <t>280779</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1072037</t>
+          <t>1072778</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1081006</t>
+          <t>1081010</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1358149</t>
+          <t>1358098</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1367350</t>
+          <t>1367282</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11834</t>
+          <t>11444</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29317</t>
+          <t>30065</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14503</t>
+          <t>14177</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34878</t>
+          <t>35004</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,7 +8111,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30318</t>
+          <t>29794</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>56059</t>
+          <t>56209</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3356405</t>
+          <t>3355657</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3373888</t>
+          <t>3374278</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3496718</t>
+          <t>3496592</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3517093</t>
+          <t>3517419</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6861259</t>
+          <t>6861109</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6887000</t>
+          <t>6887524</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8264,7 +8264,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3018</t>
+          <t>2644</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19461</t>
+          <t>19244</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6567</t>
+          <t>6901</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13457</t>
+          <t>13006</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>13759</t>
+          <t>13969</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7974</t>
+          <t>7619</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27644</t>
+          <t>25019</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>498020</t>
+          <t>543549</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>485751</t>
+          <t>531374</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>502194</t>
+          <t>547974</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>440900</t>
+          <t>481510</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>434010</t>
+          <t>475405</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>444377</t>
+          <t>485371</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>938920</t>
+          <t>1025060</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>925035</t>
+          <t>1014010</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>944705</t>
+          <t>1031410</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,102 +8976,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2996</t>
+          <t>3064</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>815</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8575</t>
+          <t>8551</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>7829</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>4174</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>13559</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>10893</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>5958</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>17526</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>0,66%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>6610</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>3080</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>11361</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>9606</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>5404</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>15819</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -9089,102 +9089,102 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>449217</t>
+          <t>480148</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>443638</t>
+          <t>474661</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>451486</t>
+          <t>482397</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
+          <t>99,37%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,23%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,83%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>579</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>415314</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>409584</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>418969</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>98,15%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>96,8%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>99,01%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1057</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>895462</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>888829</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>900397</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>98,8%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>98,07%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>99,34%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,1%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,84%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>579</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>375970</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>371219</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>379500</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,27%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>97,03%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,19%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1057</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>825187</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>818974</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>829389</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>98,85%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>98,11%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2748</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>877</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7938</t>
+          <t>9053</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1183</t>
+          <t>1249</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3954</t>
+          <t>3938</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -9379,7 +9379,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3931</t>
+          <t>4994</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8826</t>
+          <t>11119</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>665516</t>
+          <t>467867</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>660326</t>
+          <t>462559</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>668111</t>
+          <t>470735</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,98%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,27 +9467,27 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>165728</t>
+          <t>186248</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>162957</t>
+          <t>183559</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>831244</t>
+          <t>654115</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>826349</t>
+          <t>647990</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>834464</t>
+          <t>657295</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,102 +9662,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5818</t>
+          <t>6910</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2799</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12293</t>
+          <t>13367</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>11223</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>6123</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>18496</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>18134</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>11191</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>28063</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>0,56%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>10850</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>5053</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>19175</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,96%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>16668</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>9624</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>25905</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -9775,102 +9775,102 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1029001</t>
+          <t>1124933</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1022526</t>
+          <t>1118476</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1032020</t>
+          <t>1128931</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
+          <t>99,39%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,82%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,74%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>849988</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>842715</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>855088</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>98,7%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>97,85%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>99,29%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2326</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1974920</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1964991</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1981863</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>99,09%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>98,59%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>99,44%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>98,81%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1215</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>967244</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>958919</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>973041</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,89%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,04%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,48%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2326</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1996244</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1987007</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>2003288</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>99,17%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>98,71%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,7 +10005,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1962</t>
+          <t>2256</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>8251</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8949</t>
+          <t>11379</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4827</t>
+          <t>6838</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17080</t>
+          <t>18957</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>10911</t>
+          <t>13635</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6237</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18441</t>
+          <t>22540</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -10118,27 +10118,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>473084</t>
+          <t>565708</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>468376</t>
+          <t>559713</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>832386</t>
+          <t>819471</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>824255</t>
+          <t>811893</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>836508</t>
+          <t>824012</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1305470</t>
+          <t>1385179</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1297940</t>
+          <t>1376274</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1310144</t>
+          <t>1390768</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8080</t>
+          <t>8560</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t>4368</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13999</t>
+          <t>14374</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>8080</t>
+          <t>8560</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4290</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14177</t>
+          <t>14585</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -10461,7 +10461,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>753291</t>
+          <t>835721</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>747372</t>
+          <t>829907</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>757028</t>
+          <t>839913</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>993798</t>
+          <t>1072949</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>987701</t>
+          <t>1066924</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>997588</t>
+          <t>1076928</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,58%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>20716</t>
+          <t>23043</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12169</t>
+          <t>14500</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34572</t>
+          <t>35971</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>42240</t>
+          <t>47142</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31338</t>
+          <t>35449</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>56329</t>
+          <t>59421</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>62956</t>
+          <t>70185</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>48861</t>
+          <t>56153</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>80759</t>
+          <t>88964</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3355344</t>
+          <t>3419433</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3341488</t>
+          <t>3406505</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3363891</t>
+          <t>3427976</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3535518</t>
+          <t>3588251</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3521429</t>
+          <t>3575972</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3546420</t>
+          <t>3599944</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6890862</t>
+          <t>7007684</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6873059</t>
+          <t>6988905</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6904957</t>
+          <t>7021716</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
